--- a/The Ghastly Grab.xlsx
+++ b/The Ghastly Grab.xlsx
@@ -5,13 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c00313609\Desktop\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c00308560\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47212241-BE23-43C0-8778-C3ABD5D6456F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28F8EA51-CD26-4C72-A297-71141A2C9C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="e3XNt+Y+1D3+D24i3JY7ZfvaUeJ+Ficv5JqUYqK3GxA1BYB7FHhPYhxuoVdsKOXJwPbSFyACJvbToUlhxA/0dg==" workbookSaltValue="bwSytUchgVbQ5tn7OpDLYQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{B114BF61-C9F1-47F8-B51B-C5362F104DFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B114BF61-C9F1-47F8-B51B-C5362F104DFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -620,23 +620,23 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(O4:O13)</f>
-        <v>0.21000000000000002</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="P1" s="8">
         <f t="shared" ref="P1:S1" si="0">SUM(P4:P13)</f>
-        <v>0.19</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="Q1" s="8">
         <f t="shared" si="0"/>
-        <v>0.16999999999999998</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="R1" s="8">
         <f t="shared" ref="R1" si="1">SUM(R4:R13)</f>
-        <v>0.16</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="S1" s="8">
         <f t="shared" si="0"/>
-        <v>0.185</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="U1" t="s">
         <v>0</v>
@@ -742,17 +742,13 @@
         <v>0.2</v>
       </c>
       <c r="I4" s="9">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J4" s="9">
         <v>0.2</v>
       </c>
-      <c r="K4" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0.2</v>
-      </c>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
       <c r="M4" s="7">
         <f>IF(SUM(H4:L4)&lt;=1,SUM(H4:L4),"error")</f>
         <v>1</v>
@@ -763,7 +759,7 @@
       </c>
       <c r="P4" s="8">
         <f>(I4*IF($N4&gt;0,$N4,$G4)/100)</f>
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Q4" s="8">
         <f>(J4*IF($N4&gt;0,$N4,$G4)/100)</f>
@@ -771,11 +767,11 @@
       </c>
       <c r="R4" s="8">
         <f>(K4*IF($N4&gt;0,$N4,$G4)/100)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="S4" s="8">
         <f>(L4*IF($N4&gt;0,$N4,$G4)/100)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -808,7 +804,9 @@
       <c r="I5" s="9">
         <v>0.25</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="J5" s="9">
+        <v>0.05</v>
+      </c>
       <c r="K5" s="9">
         <v>0.25</v>
       </c>
@@ -817,7 +815,7 @@
       </c>
       <c r="M5" s="7">
         <f t="shared" ref="M5:M13" si="4">IF(SUM(H5:L5)&lt;=1,SUM(H5:L5),"error")</f>
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="O5" s="8">
         <f t="shared" ref="O5:O13" si="5">(H5*IF($N5&gt;0,$N5,$G5)/100)</f>
@@ -829,7 +827,7 @@
       </c>
       <c r="Q5" s="8">
         <f t="shared" ref="Q5:Q13" si="7">(J5*IF($N5&gt;0,$N5,$G5)/100)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R5" s="8">
         <f t="shared" ref="R5:R13" si="8">(K5*IF($N5&gt;0,$N5,$G5)/100)</f>
@@ -869,13 +867,13 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="7">
         <f t="shared" si="4"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="5"/>
@@ -887,7 +885,7 @@
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="7"/>
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="R6" s="8">
         <f t="shared" si="8"/>
@@ -980,12 +978,14 @@
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="J8" s="9">
+        <v>1</v>
+      </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="5"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="Q8" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R8" s="8">
         <f t="shared" si="8"/>
@@ -1033,15 +1033,17 @@
         <v>20</v>
       </c>
       <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="I9" s="9">
+        <v>0.05</v>
+      </c>
       <c r="J9" s="9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L9" s="9">
         <v>0.4</v>
-      </c>
-      <c r="L9" s="9">
-        <v>0.3</v>
       </c>
       <c r="M9" s="7">
         <f t="shared" si="4"/>
@@ -1053,19 +1055,19 @@
       </c>
       <c r="P9" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q9" s="8">
         <f t="shared" si="7"/>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R9" s="8">
         <f t="shared" si="8"/>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="S9" s="8">
         <f t="shared" si="9"/>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -1093,37 +1095,43 @@
         <v>20</v>
       </c>
       <c r="H10" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="I10" s="9">
         <v>0.4</v>
       </c>
-      <c r="I10" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
+      <c r="J10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0.1</v>
+      </c>
       <c r="M10" s="7">
         <f t="shared" si="4"/>
-        <v>0.9</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="5"/>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="P10" s="8">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="Q10" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R10" s="8">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S10" s="8">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -1269,13 +1277,13 @@
         <v>8</v>
       </c>
       <c r="H13" s="9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M13" s="7">
         <f t="shared" si="4"/>
@@ -1283,7 +1291,7 @@
       </c>
       <c r="O13" s="8">
         <f t="shared" si="5"/>
-        <v>0.04</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="P13" s="8">
         <f t="shared" si="6"/>
@@ -1299,7 +1307,7 @@
       </c>
       <c r="S13" s="8">
         <f t="shared" si="9"/>
-        <v>0.04</v>
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">

--- a/The Ghastly Grab.xlsx
+++ b/The Ghastly Grab.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c00308560\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28F8EA51-CD26-4C72-A297-71141A2C9C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{7C5F5ED7-CE48-4328-8684-3D71107E9B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3122B48-962E-4394-909C-46AD9A2553EE}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="e3XNt+Y+1D3+D24i3JY7ZfvaUeJ+Ficv5JqUYqK3GxA1BYB7FHhPYhxuoVdsKOXJwPbSFyACJvbToUlhxA/0dg==" workbookSaltValue="bwSytUchgVbQ5tn7OpDLYQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B114BF61-C9F1-47F8-B51B-C5362F104DFD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B114BF61-C9F1-47F8-B51B-C5362F104DFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,6 +39,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
+    <t>The Ghastly Grab</t>
+  </si>
+  <si>
+    <t>by Team 8 (5xWinners)</t>
+  </si>
+  <si>
     <t>want 20-30% each</t>
   </si>
   <si>
@@ -52,6 +60,9 @@
     <t>D%</t>
   </si>
   <si>
+    <t>E%</t>
+  </si>
+  <si>
     <t>total</t>
   </si>
   <si>
@@ -67,6 +78,9 @@
     <t>D</t>
   </si>
   <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>Game Element</t>
   </si>
   <si>
@@ -139,53 +153,41 @@
     <t>Team Member A</t>
   </si>
   <si>
+    <t>Daemon</t>
+  </si>
+  <si>
     <t>Team Member B</t>
   </si>
   <si>
+    <t>Filip</t>
+  </si>
+  <si>
     <t>Team Member C</t>
   </si>
   <si>
+    <t>Kevin</t>
+  </si>
+  <si>
     <t>Team Member D</t>
   </si>
   <si>
+    <t>Marie-Elise</t>
+  </si>
+  <si>
     <t>Team Member E</t>
   </si>
   <si>
+    <t>Padraig</t>
+  </si>
+  <si>
     <t>Team Member F</t>
-  </si>
-  <si>
-    <t>E%</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Daemon</t>
-  </si>
-  <si>
-    <t>Filip</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Marie-Elise</t>
-  </si>
-  <si>
-    <t>Padraig</t>
-  </si>
-  <si>
-    <t>The Ghastly Grab</t>
-  </si>
-  <si>
-    <t>by Team 8 (5xWinners)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,7 +604,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1AE6D3-2084-479B-AB85-13952D070B1F}">
   <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="2" width="23.140625" customWidth="1"/>
     <col min="6" max="6" width="5.7109375" customWidth="1"/>
@@ -611,24 +613,24 @@
     <col min="15" max="19" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="O1" s="8">
         <f>SUM(O4:O13)</f>
-        <v>0.19800000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="P1" s="8">
         <f t="shared" ref="P1:S1" si="0">SUM(P4:P13)</f>
-        <v>0.19999999999999998</v>
+        <v>0.20249999999999999</v>
       </c>
       <c r="Q1" s="8">
         <f t="shared" si="0"/>
-        <v>0.19500000000000001</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="R1" s="8">
         <f t="shared" ref="R1" si="1">SUM(R4:R13)</f>
@@ -636,13 +638,13 @@
       </c>
       <c r="S1" s="8">
         <f t="shared" si="0"/>
-        <v>0.20699999999999999</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="U1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="C2">
         <f>SUM(C4:C23)</f>
         <v>50</v>
@@ -656,54 +658,54 @@
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="M2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="str">
@@ -711,15 +713,15 @@
         <v>Value</v>
       </c>
       <c r="O3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -745,9 +747,11 @@
         <v>0.6</v>
       </c>
       <c r="J4" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="K4" s="9"/>
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0.1</v>
+      </c>
       <c r="L4" s="9"/>
       <c r="M4" s="7">
         <f>IF(SUM(H4:L4)&lt;=1,SUM(H4:L4),"error")</f>
@@ -763,23 +767,23 @@
       </c>
       <c r="Q4" s="8">
         <f>(J4*IF($N4&gt;0,$N4,$G4)/100)</f>
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="R4" s="8">
         <f>(K4*IF($N4&gt;0,$N4,$G4)/100)</f>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="S4" s="8">
         <f>(L4*IF($N4&gt;0,$N4,$G4)/100)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -799,19 +803,17 @@
         <v>20</v>
       </c>
       <c r="H5" s="9">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I5" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0.05</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="J5" s="9"/>
       <c r="K5" s="9">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="L5" s="9">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="M5" s="7">
         <f t="shared" ref="M5:M13" si="4">IF(SUM(H5:L5)&lt;=1,SUM(H5:L5),"error")</f>
@@ -819,31 +821,31 @@
       </c>
       <c r="O5" s="8">
         <f t="shared" ref="O5:O13" si="5">(H5*IF($N5&gt;0,$N5,$G5)/100)</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" ref="P5:P13" si="6">(I5*IF($N5&gt;0,$N5,$G5)/100)</f>
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" ref="Q5:Q13" si="7">(J5*IF($N5&gt;0,$N5,$G5)/100)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R5" s="8">
         <f t="shared" ref="R5:R13" si="8">(K5*IF($N5&gt;0,$N5,$G5)/100)</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" ref="S5:S13" si="9">(L5*IF($N5&gt;0,$N5,$G5)/100)</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -863,29 +865,33 @@
         <v>5</v>
       </c>
       <c r="H6" s="9">
-        <v>0.4</v>
-      </c>
-      <c r="I6" s="9"/>
+        <v>0.15</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0.15</v>
+      </c>
       <c r="J6" s="9">
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="L6" s="9">
+        <v>0.15</v>
+      </c>
       <c r="M6" s="7">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="5"/>
-        <v>0.02</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="7"/>
-        <v>0.03</v>
+        <v>2.75E-2</v>
       </c>
       <c r="R6" s="8">
         <f t="shared" si="8"/>
@@ -893,21 +899,21 @@
       </c>
       <c r="S6" s="8">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -918,22 +924,24 @@
       </c>
       <c r="G7">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="H7" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0.5</v>
+      </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="9">
-        <v>1</v>
-      </c>
-      <c r="L7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9">
+        <v>0.5</v>
+      </c>
       <c r="M7" s="7">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O7" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="6"/>
@@ -945,25 +953,25 @@
       </c>
       <c r="R7" s="8">
         <f t="shared" si="8"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="S7" s="8">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -974,22 +982,28 @@
       </c>
       <c r="G8">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="H8" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.5</v>
+      </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9">
-        <v>1</v>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
+        <v>0.4</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0.05</v>
+      </c>
       <c r="M8" s="7">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P8" s="8">
         <f t="shared" si="6"/>
@@ -997,23 +1011,23 @@
       </c>
       <c r="Q8" s="8">
         <f t="shared" si="7"/>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R8" s="8">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="S8" s="8">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -1037,10 +1051,10 @@
         <v>0.05</v>
       </c>
       <c r="J9" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K9" s="9">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="L9" s="9">
         <v>0.4</v>
@@ -1059,23 +1073,23 @@
       </c>
       <c r="Q9" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R9" s="8">
         <f t="shared" si="8"/>
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="S9" s="8">
         <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -1095,10 +1109,10 @@
         <v>20</v>
       </c>
       <c r="H10" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="9">
         <v>0.3</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0.4</v>
       </c>
       <c r="J10" s="9">
         <v>0.1</v>
@@ -1115,11 +1129,11 @@
       </c>
       <c r="O10" s="8">
         <f t="shared" si="5"/>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="P10" s="8">
         <f t="shared" si="6"/>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="Q10" s="8">
         <f t="shared" si="7"/>
@@ -1134,12 +1148,12 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1158,18 +1172,16 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="H11" s="9">
-        <v>0.2</v>
-      </c>
+      <c r="H11" s="9"/>
       <c r="I11" s="9">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="J11" s="9">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" si="4"/>
@@ -1177,15 +1189,15 @@
       </c>
       <c r="O11" s="8">
         <f t="shared" si="5"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P11" s="8">
         <f t="shared" si="6"/>
-        <v>0.03</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q11" s="8">
         <f t="shared" si="7"/>
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="R11" s="8">
         <f t="shared" si="8"/>
@@ -1193,15 +1205,15 @@
       </c>
       <c r="S11" s="8">
         <f t="shared" si="9"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1252,18 +1264,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13" s="6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>20</v>
@@ -1274,24 +1286,20 @@
       </c>
       <c r="G13">
         <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="H13" s="9">
-        <v>0.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="9">
-        <v>0.4</v>
-      </c>
+      <c r="L13" s="9"/>
       <c r="M13" s="7">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="5"/>
-        <v>4.8000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <f t="shared" si="6"/>
@@ -1307,52 +1315,52 @@
       </c>
       <c r="S13" s="8">
         <f t="shared" si="9"/>
-        <v>3.2000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="4" t="s">
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>36</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
